--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -857,7 +857,7 @@
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="10" max="10" width="24.6640625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,6 +199,18 @@
   </si>
   <si>
     <t>MCA [D21P2635]</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>not satisfied</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>I am not satisfied what I am doing</t>
   </si>
 </sst>
 </file>
@@ -1024,27 +1036,51 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B7" s="14">
+        <v>496</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>480</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>45</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1251</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>189</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,66 @@
   </si>
   <si>
     <t>I am not satisfied what I am doing</t>
+  </si>
+  <si>
+    <t>not well</t>
+  </si>
+  <si>
+    <t>quite low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not satisfied yet </t>
+  </si>
+  <si>
+    <t>quite good</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>trying to do</t>
+  </si>
+  <si>
+    <t>trying</t>
+  </si>
+  <si>
+    <t>frustrted</t>
+  </si>
+  <si>
+    <t>hurried</t>
+  </si>
+  <si>
+    <t>felling well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trying </t>
+  </si>
+  <si>
+    <t>relex</t>
+  </si>
+  <si>
+    <t>day is quite good</t>
+  </si>
+  <si>
+    <t>doing things</t>
+  </si>
+  <si>
+    <t>day quite good</t>
+  </si>
+  <si>
+    <t>doing good</t>
+  </si>
+  <si>
+    <t>trying to go</t>
+  </si>
+  <si>
+    <t>lazy</t>
+  </si>
+  <si>
+    <t>fine</t>
+  </si>
+  <si>
+    <t>doing and trying</t>
   </si>
 </sst>
 </file>
@@ -1083,356 +1143,740 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>25</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>40</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>685</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>755</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>20</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>20</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>49</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>829</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>611</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B10" s="14">
+        <v>425</v>
+      </c>
+      <c r="C10" s="14">
+        <v>15</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>20</v>
+      </c>
+      <c r="F10" s="14">
+        <v>225</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>40</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>25</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>45</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B12" s="14">
+        <v>400</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>150</v>
+      </c>
+      <c r="E12" s="14">
+        <v>25</v>
+      </c>
+      <c r="F12" s="14">
+        <v>335</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>100</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>400</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>40</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>50</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="14">
+        <v>45</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>685</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>755</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>200</v>
+      </c>
+      <c r="E15" s="14">
+        <v>20</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>40</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>225</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>40</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>20</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>40</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>25</v>
+      </c>
+      <c r="F19" s="14">
+        <v>335</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>400</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>40</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>40</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>25</v>
+      </c>
+      <c r="D22" s="14">
+        <v>100</v>
+      </c>
+      <c r="E22" s="14">
+        <v>25</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>45</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>615</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>825</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>25</v>
+      </c>
+      <c r="D23" s="14">
+        <v>100</v>
+      </c>
+      <c r="E23" s="14">
+        <v>25</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>40</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -201,9 +201,6 @@
     <t>MCA [D21P2635]</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
     <t>not satisfied</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t xml:space="preserve">not satisfied yet </t>
   </si>
   <si>
-    <t>quite good</t>
-  </si>
-  <si>
     <t>medium</t>
   </si>
   <si>
@@ -237,16 +231,7 @@
     <t>frustrted</t>
   </si>
   <si>
-    <t>hurried</t>
-  </si>
-  <si>
-    <t>felling well</t>
-  </si>
-  <si>
     <t xml:space="preserve">trying </t>
-  </si>
-  <si>
-    <t>relex</t>
   </si>
   <si>
     <t>day is quite good</t>
@@ -265,9 +250,6 @@
   </si>
   <si>
     <t>lazy</t>
-  </si>
-  <si>
-    <t>fine</t>
   </si>
   <si>
     <t>doing and trying</t>
@@ -1129,17 +1111,17 @@
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="16">
+        <v>4</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1175,17 +1157,17 @@
         <f t="shared" si="1"/>
         <v>755</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="16">
+        <v>2</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1221,17 +1203,17 @@
         <f t="shared" si="1"/>
         <v>611</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="16">
+        <v>3</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1267,17 +1249,17 @@
         <f t="shared" si="1"/>
         <v>595</v>
       </c>
-      <c r="K10" s="16" t="s">
-        <v>56</v>
+      <c r="K10" s="16">
+        <v>4</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1313,17 +1295,17 @@
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="16">
+        <v>4</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M11" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1359,17 +1341,17 @@
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>68</v>
+      <c r="K12" s="16">
+        <v>2</v>
       </c>
       <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1405,17 +1387,17 @@
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K13" s="16" t="s">
-        <v>58</v>
+      <c r="K13" s="16">
+        <v>1</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1451,17 +1433,17 @@
         <f t="shared" si="1"/>
         <v>755</v>
       </c>
-      <c r="K14" s="16" t="s">
-        <v>69</v>
+      <c r="K14" s="16">
+        <v>3</v>
       </c>
       <c r="L14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1497,17 +1479,17 @@
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
-      <c r="K15" s="16" t="s">
-        <v>71</v>
+      <c r="K15" s="16">
+        <v>3</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1543,17 +1525,17 @@
         <f t="shared" si="1"/>
         <v>615</v>
       </c>
-      <c r="K16" s="16" t="s">
-        <v>56</v>
+      <c r="K16" s="16">
+        <v>3</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1589,17 +1571,17 @@
         <f t="shared" si="1"/>
         <v>585</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="16">
+        <v>3</v>
+      </c>
+      <c r="L17" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="M17" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1635,17 +1617,17 @@
         <f t="shared" si="1"/>
         <v>520</v>
       </c>
-      <c r="K18" s="16" t="s">
-        <v>58</v>
+      <c r="K18" s="16">
+        <v>2</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1681,17 +1663,17 @@
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K19" s="16" t="s">
-        <v>56</v>
+      <c r="K19" s="16">
+        <v>4</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1727,17 +1709,17 @@
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K20" s="16" t="s">
-        <v>56</v>
+      <c r="K20" s="16">
+        <v>4</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1773,17 +1755,17 @@
         <f t="shared" si="1"/>
         <v>820</v>
       </c>
-      <c r="K21" s="16" t="s">
-        <v>77</v>
+      <c r="K21" s="16">
+        <v>2</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1819,17 +1801,17 @@
         <f t="shared" si="1"/>
         <v>825</v>
       </c>
-      <c r="K22" s="16" t="s">
-        <v>77</v>
+      <c r="K22" s="16">
+        <v>2</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1865,17 +1847,17 @@
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="K23" s="16" t="s">
-        <v>78</v>
+      <c r="K23" s="16">
+        <v>3</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -201,9 +201,6 @@
     <t>MCA [D21P2635]</t>
   </si>
   <si>
-    <t>not satisfied</t>
-  </si>
-  <si>
     <t>low</t>
   </si>
   <si>
@@ -237,13 +234,7 @@
     <t>day is quite good</t>
   </si>
   <si>
-    <t>doing things</t>
-  </si>
-  <si>
     <t>day quite good</t>
-  </si>
-  <si>
-    <t>doing good</t>
   </si>
   <si>
     <t>trying to go</t>
@@ -1114,14 +1105,14 @@
       <c r="K7" s="16">
         <v>4</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="16">
+        <v>2</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="N7" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1160,14 +1151,14 @@
       <c r="K8" s="16">
         <v>2</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>56</v>
+      <c r="L8" s="16">
+        <v>2</v>
       </c>
       <c r="M8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1206,14 +1197,14 @@
       <c r="K9" s="16">
         <v>3</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>56</v>
+      <c r="L9" s="16">
+        <v>2</v>
       </c>
       <c r="M9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1252,14 +1243,14 @@
       <c r="K10" s="16">
         <v>4</v>
       </c>
-      <c r="L10" s="16" t="s">
-        <v>64</v>
+      <c r="L10" s="16">
+        <v>3</v>
       </c>
       <c r="M10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1298,14 +1289,14 @@
       <c r="K11" s="16">
         <v>4</v>
       </c>
-      <c r="L11" s="16" t="s">
-        <v>56</v>
+      <c r="L11" s="16">
+        <v>2</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1344,14 +1335,14 @@
       <c r="K12" s="16">
         <v>2</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="16">
+        <v>2</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>57</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1390,14 +1381,14 @@
       <c r="K13" s="16">
         <v>1</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>64</v>
+      <c r="L13" s="16">
+        <v>3</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1436,14 +1427,14 @@
       <c r="K14" s="16">
         <v>3</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>64</v>
+      <c r="L14" s="16">
+        <v>3</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1482,14 +1473,14 @@
       <c r="K15" s="16">
         <v>3</v>
       </c>
-      <c r="L15" s="16" t="s">
-        <v>68</v>
+      <c r="L15" s="16">
+        <v>3</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1528,14 +1519,14 @@
       <c r="K16" s="16">
         <v>3</v>
       </c>
-      <c r="L16" s="16" t="s">
-        <v>68</v>
+      <c r="L16" s="16">
+        <v>3</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1574,14 +1565,14 @@
       <c r="K17" s="16">
         <v>3</v>
       </c>
-      <c r="L17" s="16" t="s">
-        <v>56</v>
+      <c r="L17" s="16">
+        <v>2</v>
       </c>
       <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1620,14 +1611,14 @@
       <c r="K18" s="16">
         <v>2</v>
       </c>
-      <c r="L18" s="16" t="s">
-        <v>70</v>
+      <c r="L18" s="16">
+        <v>4</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1666,14 +1657,14 @@
       <c r="K19" s="16">
         <v>4</v>
       </c>
-      <c r="L19" s="16" t="s">
-        <v>70</v>
+      <c r="L19" s="16">
+        <v>4</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1712,14 +1703,14 @@
       <c r="K20" s="16">
         <v>4</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L20" s="16">
+        <v>3</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1758,14 +1749,14 @@
       <c r="K21" s="16">
         <v>2</v>
       </c>
-      <c r="L21" s="16" t="s">
-        <v>72</v>
+      <c r="L21" s="16">
+        <v>2</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1804,14 +1795,14 @@
       <c r="K22" s="16">
         <v>2</v>
       </c>
-      <c r="L22" s="16" t="s">
-        <v>72</v>
+      <c r="L22" s="16">
+        <v>2</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1850,14 +1841,14 @@
       <c r="K23" s="16">
         <v>3</v>
       </c>
-      <c r="L23" s="16" t="s">
-        <v>64</v>
+      <c r="L23" s="16">
+        <v>3</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -201,22 +201,13 @@
     <t>MCA [D21P2635]</t>
   </si>
   <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>I am not satisfied what I am doing</t>
   </si>
   <si>
     <t>not well</t>
   </si>
   <si>
-    <t>quite low</t>
-  </si>
-  <si>
     <t xml:space="preserve">not satisfied yet </t>
-  </si>
-  <si>
-    <t>medium</t>
   </si>
   <si>
     <t>trying to do</t>
@@ -1108,11 +1099,11 @@
       <c r="L7" s="16">
         <v>2</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="16">
+        <v>2</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1154,11 +1145,11 @@
       <c r="L8" s="16">
         <v>2</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>59</v>
+      <c r="M8" s="16">
+        <v>2</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1200,11 +1191,11 @@
       <c r="L9" s="16">
         <v>2</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>61</v>
+      <c r="M9" s="16">
+        <v>3</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1246,11 +1237,11 @@
       <c r="L10" s="16">
         <v>3</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>61</v>
+      <c r="M10" s="16">
+        <v>3</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1292,11 +1283,11 @@
       <c r="L11" s="16">
         <v>2</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="16">
+        <v>3</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1338,11 +1329,11 @@
       <c r="L12" s="16">
         <v>2</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>56</v>
+      <c r="M12" s="16">
+        <v>2</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1384,11 +1375,11 @@
       <c r="L13" s="16">
         <v>3</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>56</v>
+      <c r="M13" s="16">
+        <v>2</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1430,11 +1421,11 @@
       <c r="L14" s="16">
         <v>3</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>61</v>
+      <c r="M14" s="16">
+        <v>3</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1476,11 +1467,11 @@
       <c r="L15" s="16">
         <v>3</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>61</v>
+      <c r="M15" s="16">
+        <v>3</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1522,11 +1513,11 @@
       <c r="L16" s="16">
         <v>3</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>61</v>
+      <c r="M16" s="16">
+        <v>3</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1568,11 +1559,11 @@
       <c r="L17" s="16">
         <v>2</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>61</v>
+      <c r="M17" s="16">
+        <v>3</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1614,11 +1605,11 @@
       <c r="L18" s="16">
         <v>4</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>61</v>
+      <c r="M18" s="16">
+        <v>3</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1660,11 +1651,11 @@
       <c r="L19" s="16">
         <v>4</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>61</v>
+      <c r="M19" s="16">
+        <v>3</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1706,11 +1697,11 @@
       <c r="L20" s="16">
         <v>3</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>61</v>
+      <c r="M20" s="16">
+        <v>3</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1752,11 +1743,11 @@
       <c r="L21" s="16">
         <v>2</v>
       </c>
-      <c r="M21" s="16" t="s">
-        <v>61</v>
+      <c r="M21" s="16">
+        <v>3</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1798,11 +1789,11 @@
       <c r="L22" s="16">
         <v>2</v>
       </c>
-      <c r="M22" s="16" t="s">
-        <v>61</v>
+      <c r="M22" s="16">
+        <v>3</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1844,11 +1835,11 @@
       <c r="L23" s="16">
         <v>3</v>
       </c>
-      <c r="M23" s="16" t="s">
-        <v>61</v>
+      <c r="M23" s="16">
+        <v>3</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,42 +199,6 @@
   </si>
   <si>
     <t>MCA [D21P2635]</t>
-  </si>
-  <si>
-    <t>I am not satisfied what I am doing</t>
-  </si>
-  <si>
-    <t>not well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not satisfied yet </t>
-  </si>
-  <si>
-    <t>trying to do</t>
-  </si>
-  <si>
-    <t>trying</t>
-  </si>
-  <si>
-    <t>frustrted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trying </t>
-  </si>
-  <si>
-    <t>day is quite good</t>
-  </si>
-  <si>
-    <t>day quite good</t>
-  </si>
-  <si>
-    <t>trying to go</t>
-  </si>
-  <si>
-    <t>lazy</t>
-  </si>
-  <si>
-    <t>doing and trying</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1024,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46263</v>
       </c>
@@ -1102,8 +1066,8 @@
       <c r="M7" s="16">
         <v>2</v>
       </c>
-      <c r="N7" s="17" t="s">
-        <v>56</v>
+      <c r="N7" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1148,8 +1112,8 @@
       <c r="M8" s="16">
         <v>2</v>
       </c>
-      <c r="N8" s="17" t="s">
-        <v>58</v>
+      <c r="N8" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1194,8 +1158,8 @@
       <c r="M9" s="16">
         <v>3</v>
       </c>
-      <c r="N9" s="17" t="s">
-        <v>59</v>
+      <c r="N9" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1240,8 +1204,8 @@
       <c r="M10" s="16">
         <v>3</v>
       </c>
-      <c r="N10" s="17" t="s">
-        <v>59</v>
+      <c r="N10" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1286,8 +1250,8 @@
       <c r="M11" s="16">
         <v>3</v>
       </c>
-      <c r="N11" s="17" t="s">
-        <v>61</v>
+      <c r="N11" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1332,8 +1296,8 @@
       <c r="M12" s="16">
         <v>2</v>
       </c>
-      <c r="N12" s="17" t="s">
-        <v>61</v>
+      <c r="N12" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1378,8 +1342,8 @@
       <c r="M13" s="16">
         <v>2</v>
       </c>
-      <c r="N13" s="17" t="s">
-        <v>57</v>
+      <c r="N13" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1424,8 +1388,8 @@
       <c r="M14" s="16">
         <v>3</v>
       </c>
-      <c r="N14" s="17" t="s">
-        <v>62</v>
+      <c r="N14" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1470,8 +1434,8 @@
       <c r="M15" s="16">
         <v>3</v>
       </c>
-      <c r="N15" s="17" t="s">
-        <v>63</v>
+      <c r="N15" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1516,8 +1480,8 @@
       <c r="M16" s="16">
         <v>3</v>
       </c>
-      <c r="N16" s="17" t="s">
-        <v>64</v>
+      <c r="N16" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1562,8 +1526,8 @@
       <c r="M17" s="16">
         <v>3</v>
       </c>
-      <c r="N17" s="17" t="s">
-        <v>59</v>
+      <c r="N17" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1608,8 +1572,8 @@
       <c r="M18" s="16">
         <v>3</v>
       </c>
-      <c r="N18" s="17" t="s">
-        <v>58</v>
+      <c r="N18" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1654,8 +1618,8 @@
       <c r="M19" s="16">
         <v>3</v>
       </c>
-      <c r="N19" s="17" t="s">
-        <v>65</v>
+      <c r="N19" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1700,8 +1664,8 @@
       <c r="M20" s="16">
         <v>3</v>
       </c>
-      <c r="N20" s="17" t="s">
-        <v>60</v>
+      <c r="N20" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1746,8 +1710,8 @@
       <c r="M21" s="16">
         <v>3</v>
       </c>
-      <c r="N21" s="17" t="s">
-        <v>66</v>
+      <c r="N21" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1792,8 +1756,8 @@
       <c r="M22" s="16">
         <v>3</v>
       </c>
-      <c r="N22" s="17" t="s">
-        <v>66</v>
+      <c r="N22" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1838,8 +1802,8 @@
       <c r="M23" s="16">
         <v>3</v>
       </c>
-      <c r="N23" s="17" t="s">
-        <v>67</v>
+      <c r="N23" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -1807,48 +1807,96 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>225</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>40</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K24" s="16">
+        <v>3</v>
+      </c>
+      <c r="L24" s="16">
+        <v>3</v>
+      </c>
+      <c r="M24" s="16">
+        <v>3</v>
+      </c>
+      <c r="N24" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>100</v>
+      </c>
+      <c r="E25" s="14">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>40</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K25" s="16">
+        <v>3</v>
+      </c>
+      <c r="L25" s="16">
+        <v>2</v>
+      </c>
+      <c r="M25" s="16">
+        <v>3</v>
+      </c>
+      <c r="N25" s="17">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -1899,26 +1899,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>100</v>
+      </c>
+      <c r="E26" s="14">
+        <v>20</v>
+      </c>
+      <c r="F26" s="14">
+        <v>335</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>40</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K26" s="16">
+        <v>3</v>
+      </c>
+      <c r="L26" s="16">
+        <v>3</v>
+      </c>
+      <c r="M26" s="16">
+        <v>2</v>
+      </c>
+      <c r="N26" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -310,7 +310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -333,11 +333,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -381,11 +392,47 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -848,7 +895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.77734375" customWidth="1"/>
@@ -864,7 +911,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -882,7 +929,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -899,7 +946,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -916,7 +963,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -934,7 +981,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -978,7 +1025,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1024,7 +1071,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46263</v>
       </c>
@@ -1070,7 +1117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>46264</v>
       </c>
@@ -1116,7 +1163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>46265</v>
       </c>
@@ -1162,7 +1209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46266</v>
       </c>
@@ -1208,7 +1255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46267</v>
       </c>
@@ -1254,7 +1301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46268</v>
       </c>
@@ -1300,7 +1347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46269</v>
       </c>
@@ -1346,7 +1393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46270</v>
       </c>
@@ -1391,8 +1438,11 @@
       <c r="N14" s="17">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46271</v>
       </c>
@@ -1438,7 +1488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46272</v>
       </c>
@@ -1945,180 +1995,372 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>25</v>
+      </c>
+      <c r="F27" s="14">
+        <v>335</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>40</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" ref="I27:I34" si="2">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <v>960</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" ref="J27:J34" si="3">IF(I27="","",1440-I27)</f>
+        <v>480</v>
+      </c>
+      <c r="K27" s="16">
+        <v>4</v>
+      </c>
+      <c r="L27" s="16">
+        <v>4</v>
+      </c>
+      <c r="M27" s="16">
+        <v>3</v>
+      </c>
+      <c r="N27" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="A28" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>400</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>40</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="K28" s="16">
+        <v>4</v>
+      </c>
+      <c r="L28" s="16">
+        <v>3</v>
+      </c>
+      <c r="M28" s="16">
+        <v>3</v>
+      </c>
+      <c r="N28" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="A29" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>20</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="2"/>
+        <v>620</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="3"/>
+        <v>820</v>
+      </c>
+      <c r="K29" s="16">
+        <v>2</v>
+      </c>
+      <c r="L29" s="16">
+        <v>2</v>
+      </c>
+      <c r="M29" s="16">
+        <v>3</v>
+      </c>
+      <c r="N29" s="17">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="A30" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>25</v>
+      </c>
+      <c r="D30" s="14">
+        <v>100</v>
+      </c>
+      <c r="E30" s="14">
+        <v>25</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>45</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" si="2"/>
+        <v>615</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="3"/>
+        <v>825</v>
+      </c>
+      <c r="K30" s="16">
+        <v>2</v>
+      </c>
+      <c r="L30" s="16">
+        <v>2</v>
+      </c>
+      <c r="M30" s="16">
+        <v>3</v>
+      </c>
+      <c r="N30" s="17">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="A31" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>25</v>
+      </c>
+      <c r="D31" s="14">
+        <v>100</v>
+      </c>
+      <c r="E31" s="14">
+        <v>25</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>40</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="K31" s="16">
+        <v>3</v>
+      </c>
+      <c r="L31" s="16">
+        <v>3</v>
+      </c>
+      <c r="M31" s="16">
+        <v>3</v>
+      </c>
+      <c r="N31" s="17">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="A32" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>20</v>
+      </c>
+      <c r="F32" s="14">
+        <v>225</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="2"/>
+        <v>845</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="3"/>
+        <v>595</v>
+      </c>
+      <c r="K32" s="16">
+        <v>3</v>
+      </c>
+      <c r="L32" s="16">
+        <v>3</v>
+      </c>
+      <c r="M32" s="16">
+        <v>3</v>
+      </c>
+      <c r="N32" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="A33" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>100</v>
+      </c>
+      <c r="E33" s="14">
+        <v>25</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>40</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="2"/>
+        <v>905</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="3"/>
+        <v>535</v>
+      </c>
+      <c r="K33" s="16">
+        <v>3</v>
+      </c>
+      <c r="L33" s="16">
+        <v>2</v>
+      </c>
+      <c r="M33" s="16">
+        <v>3</v>
+      </c>
+      <c r="N33" s="17">
+        <v>2</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="A34" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>100</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>335</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>40</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="2"/>
+        <v>935</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="3"/>
+        <v>505</v>
+      </c>
+      <c r="K34" s="16">
+        <v>3</v>
+      </c>
+      <c r="L34" s="16">
+        <v>3</v>
+      </c>
+      <c r="M34" s="16">
+        <v>2</v>
+      </c>
+      <c r="N34" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
@@ -2900,11 +3142,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2922,11 +3164,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2944,11 +3186,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2966,11 +3208,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2988,11 +3230,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3010,11 +3252,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3032,11 +3274,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3054,11 +3296,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3076,11 +3318,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3098,11 +3340,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3120,11 +3362,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3142,11 +3384,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3164,11 +3406,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3186,11 +3428,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3208,11 +3450,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3230,11 +3472,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3252,11 +3494,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3274,11 +3516,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3296,11 +3538,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3318,11 +3560,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3340,11 +3582,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3362,11 +3604,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3384,11 +3626,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3406,11 +3648,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3428,11 +3670,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3450,11 +3692,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3472,11 +3714,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3494,11 +3736,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3516,11 +3758,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3538,11 +3780,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3560,11 +3802,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3582,11 +3824,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3604,11 +3846,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3626,11 +3868,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3648,11 +3890,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3670,11 +3912,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3692,11 +3934,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3714,11 +3956,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3736,11 +3978,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3758,11 +4000,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3780,11 +4022,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3802,11 +4044,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3824,11 +4066,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3846,11 +4088,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3868,11 +4110,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3890,11 +4132,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3912,11 +4154,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3934,11 +4176,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3956,11 +4198,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3978,11 +4220,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4000,11 +4242,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4022,11 +4264,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4044,11 +4286,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4066,11 +4308,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4088,11 +4330,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4110,11 +4352,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4132,11 +4374,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4154,11 +4396,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4176,11 +4418,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4198,11 +4440,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4220,11 +4462,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4242,11 +4484,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4264,11 +4506,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4286,11 +4528,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4308,11 +4550,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4330,11 +4572,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4352,11 +4594,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4374,11 +4616,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4396,11 +4638,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4418,11 +4660,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4440,11 +4682,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4462,11 +4704,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4484,11 +4726,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4506,11 +4748,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4528,11 +4770,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4550,11 +4792,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4572,11 +4814,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4594,11 +4836,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4616,11 +4858,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4638,11 +4880,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4660,11 +4902,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4682,11 +4924,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4704,11 +4946,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4726,11 +4968,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4748,11 +4990,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4770,11 +5012,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4792,11 +5034,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4814,11 +5056,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4836,11 +5078,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4858,11 +5100,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4880,11 +5122,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4902,11 +5144,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4924,11 +5166,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4946,11 +5188,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4968,11 +5210,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4990,11 +5232,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5012,11 +5254,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5034,11 +5276,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5056,11 +5298,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5078,11 +5320,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5100,11 +5342,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5122,11 +5364,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5144,11 +5386,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5166,11 +5408,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5188,11 +5430,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5210,11 +5452,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5232,11 +5474,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5254,11 +5496,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5276,11 +5518,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5298,11 +5540,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5320,11 +5562,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5342,11 +5584,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5364,11 +5606,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5386,11 +5628,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5408,11 +5650,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5430,11 +5672,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5452,11 +5694,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5474,11 +5716,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5496,11 +5738,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5518,11 +5760,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5540,11 +5782,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5562,11 +5804,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5584,11 +5826,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5606,11 +5848,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5628,11 +5870,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5650,11 +5892,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5672,11 +5914,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5694,11 +5936,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5716,11 +5958,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5738,11 +5980,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5760,11 +6002,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5782,11 +6024,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5804,11 +6046,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5826,11 +6068,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5848,11 +6090,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5870,11 +6112,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5892,11 +6134,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5914,11 +6156,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5936,11 +6178,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5958,11 +6200,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5980,11 +6222,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6002,11 +6244,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6024,11 +6266,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6046,11 +6288,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6068,11 +6310,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6090,11 +6332,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6112,11 +6354,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6134,11 +6376,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6156,11 +6398,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6178,11 +6420,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6200,11 +6442,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6222,11 +6464,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6244,11 +6486,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6266,11 +6508,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6288,11 +6530,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6310,11 +6552,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6332,11 +6574,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6354,11 +6596,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6376,11 +6618,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6398,11 +6640,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6420,11 +6662,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6442,11 +6684,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6464,11 +6706,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6486,11 +6728,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6508,11 +6750,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6530,11 +6772,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6552,11 +6794,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6574,11 +6816,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6596,11 +6838,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6618,11 +6860,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6640,11 +6882,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6662,11 +6904,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6684,11 +6926,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6706,11 +6948,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6728,11 +6970,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6750,11 +6992,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6772,11 +7014,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6794,11 +7036,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6816,11 +7058,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6838,11 +7080,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6860,11 +7102,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6882,11 +7124,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6904,11 +7146,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6926,11 +7168,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6948,11 +7190,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6970,11 +7212,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6992,11 +7234,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7014,11 +7256,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7036,11 +7278,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7058,11 +7300,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7080,11 +7322,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7102,11 +7344,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7124,11 +7366,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7146,11 +7388,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7168,11 +7410,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7190,11 +7432,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7212,11 +7454,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7234,11 +7476,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7256,11 +7498,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7278,11 +7520,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7300,11 +7542,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7322,11 +7564,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7344,11 +7586,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7366,11 +7608,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7388,11 +7630,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7410,11 +7652,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7432,11 +7674,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7454,11 +7696,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7476,11 +7718,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7498,11 +7740,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7520,11 +7762,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7542,11 +7784,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7564,11 +7806,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7586,11 +7828,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7608,11 +7850,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7630,11 +7872,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7652,11 +7894,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7674,11 +7916,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7696,11 +7938,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7718,11 +7960,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7740,11 +7982,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7762,11 +8004,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7784,11 +8026,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7806,11 +8048,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7828,11 +8070,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7850,11 +8092,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7872,11 +8114,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7894,11 +8136,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7916,11 +8158,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7938,11 +8180,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7960,11 +8202,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7982,11 +8224,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8004,11 +8246,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8026,11 +8268,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8048,11 +8290,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8070,11 +8312,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8092,11 +8334,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8114,11 +8356,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8136,11 +8378,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8158,11 +8400,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8180,11 +8422,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8202,11 +8444,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8224,11 +8466,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8246,11 +8488,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8268,11 +8510,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8290,11 +8532,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8312,11 +8554,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8334,11 +8576,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8356,11 +8598,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8378,11 +8620,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8400,11 +8642,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8422,11 +8664,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8444,11 +8686,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8466,11 +8708,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8488,11 +8730,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8510,11 +8752,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8532,11 +8774,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8554,11 +8796,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8576,11 +8818,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8598,11 +8840,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8620,11 +8862,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8642,11 +8884,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8664,11 +8906,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8686,11 +8928,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8708,11 +8950,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8730,11 +8972,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8752,11 +8994,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8774,11 +9016,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8796,11 +9038,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8818,11 +9060,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8840,11 +9082,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8862,11 +9104,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8884,11 +9126,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8906,11 +9148,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8928,11 +9170,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8950,11 +9192,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8972,11 +9214,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8994,11 +9236,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9016,11 +9258,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9038,11 +9280,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9060,11 +9302,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9082,11 +9324,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9104,11 +9346,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9126,11 +9368,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9148,11 +9390,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9170,11 +9412,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9192,11 +9434,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9214,11 +9456,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9236,11 +9478,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9258,11 +9500,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9280,11 +9522,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9302,11 +9544,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9324,11 +9566,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9346,11 +9588,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9368,11 +9610,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9390,11 +9632,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9412,11 +9654,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9434,11 +9676,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9456,11 +9698,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9478,11 +9720,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9500,11 +9742,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9522,11 +9764,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9544,11 +9786,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9566,11 +9808,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9588,11 +9830,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9610,11 +9852,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9632,11 +9874,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9654,11 +9896,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9676,11 +9918,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9698,11 +9940,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9720,11 +9962,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9742,11 +9984,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9764,11 +10006,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9786,11 +10028,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9808,11 +10050,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9830,11 +10072,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9852,11 +10094,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9874,11 +10116,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9896,11 +10138,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9918,11 +10160,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9940,11 +10182,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9962,11 +10204,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9984,11 +10226,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10006,11 +10248,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10028,11 +10270,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10050,11 +10292,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10072,11 +10314,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10094,11 +10336,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10116,11 +10358,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10138,11 +10380,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10160,11 +10402,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10182,11 +10424,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10203,8 +10445,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J26 J35:J401">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27:J34">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -399,7 +399,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1071,87 +1082,87 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B7" s="14">
-        <v>496</v>
-      </c>
-      <c r="C7" s="14">
-        <v>20</v>
-      </c>
-      <c r="D7" s="14">
+    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46223</v>
+      </c>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>45</v>
+      </c>
+      <c r="D7" s="9">
+        <v>120</v>
+      </c>
+      <c r="E7" s="9">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9">
         <v>180</v>
       </c>
-      <c r="E7" s="14">
+      <c r="G7" s="9">
+        <v>3</v>
+      </c>
+      <c r="H7" s="9">
         <v>30</v>
       </c>
-      <c r="F7" s="14">
-        <v>480</v>
-      </c>
-      <c r="G7" s="14">
-        <v>7</v>
-      </c>
-      <c r="H7" s="14">
-        <v>45</v>
-      </c>
-      <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>1251</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>189</v>
-      </c>
-      <c r="K7" s="16">
-        <v>4</v>
-      </c>
-      <c r="L7" s="16">
-        <v>2</v>
-      </c>
-      <c r="M7" s="16">
-        <v>2</v>
-      </c>
-      <c r="N7" s="17">
-        <v>2</v>
+      <c r="I7" s="10">
+        <f t="shared" ref="I7:I15" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>885</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" ref="J7:J15" si="3">IF(I7="","",1440-I7)</f>
+        <v>555</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B8" s="14">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="C8" s="14">
         <v>20</v>
       </c>
       <c r="D8" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E8" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F8" s="14">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G8" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H8" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>685</v>
+        <f t="shared" si="2"/>
+        <v>1251</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>755</v>
+        <f t="shared" si="3"/>
+        <v>189</v>
       </c>
       <c r="K8" s="16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="16">
         <v>2</v>
@@ -1165,10 +1176,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B9" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
@@ -1177,47 +1188,47 @@
         <v>120</v>
       </c>
       <c r="E9" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>829</v>
+        <f t="shared" si="2"/>
+        <v>685</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>611</v>
+        <f t="shared" si="3"/>
+        <v>755</v>
       </c>
       <c r="K9" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="16">
         <v>2</v>
       </c>
       <c r="M9" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B10" s="14">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C10" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" s="14">
         <v>120</v>
@@ -1226,27 +1237,27 @@
         <v>20</v>
       </c>
       <c r="F10" s="14">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G10" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>845</v>
+        <f t="shared" si="2"/>
+        <v>829</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>595</v>
+        <f t="shared" si="3"/>
+        <v>611</v>
       </c>
       <c r="K10" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10" s="16">
         <v>3</v>
@@ -1257,91 +1268,91 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B11" s="14">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C11" s="14">
+        <v>15</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
         <v>20</v>
       </c>
-      <c r="D11" s="14">
-        <v>100</v>
-      </c>
-      <c r="E11" s="14">
-        <v>25</v>
-      </c>
       <c r="F11" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="G11" s="14">
         <v>5</v>
       </c>
       <c r="H11" s="14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>910</v>
+        <f t="shared" si="2"/>
+        <v>845</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>530</v>
+        <f t="shared" si="3"/>
+        <v>595</v>
       </c>
       <c r="K11" s="16">
         <v>4</v>
       </c>
       <c r="L11" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="16">
         <v>3</v>
       </c>
       <c r="N11" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B12" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
         <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E12" s="14">
         <v>25</v>
       </c>
       <c r="F12" s="14">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="G12" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f t="shared" si="2"/>
+        <v>910</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f t="shared" si="3"/>
+        <v>530</v>
       </c>
       <c r="K12" s="16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" s="16">
         <v>2</v>
       </c>
       <c r="M12" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="17">
         <v>2</v>
@@ -1349,102 +1360,99 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B13" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C13" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E13" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13" s="14">
-        <v>400</v>
+        <v>335</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>960</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
       <c r="K13" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" s="16">
         <v>2</v>
       </c>
       <c r="N13" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B14" s="14">
         <v>420</v>
       </c>
       <c r="C14" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D14" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E14" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>40</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="2"/>
+        <v>960</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="K14" s="16">
         <v>1</v>
-      </c>
-      <c r="H14" s="14">
-        <v>45</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>685</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>755</v>
-      </c>
-      <c r="K14" s="16">
-        <v>3</v>
       </c>
       <c r="L14" s="16">
         <v>3</v>
       </c>
       <c r="M14" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" s="17">
         <v>3</v>
       </c>
-      <c r="O14" s="21">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B15" s="14">
         <v>420</v>
@@ -1453,27 +1461,27 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G15" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>710</v>
+        <f t="shared" si="2"/>
+        <v>685</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>730</v>
+        <f t="shared" si="3"/>
+        <v>755</v>
       </c>
       <c r="K15" s="16">
         <v>3</v>
@@ -1485,7 +1493,10 @@
         <v>3</v>
       </c>
       <c r="N15" s="17">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="O15" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -2020,11 +2031,11 @@
         <v>40</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" ref="I27:I34" si="2">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <f t="shared" ref="I27:I34" si="4">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
         <v>960</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" ref="J27:J34" si="3">IF(I27="","",1440-I27)</f>
+        <f t="shared" ref="J27:J34" si="5">IF(I27="","",1440-I27)</f>
         <v>480</v>
       </c>
       <c r="K27" s="16">
@@ -2066,11 +2077,11 @@
         <v>40</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1030</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>410</v>
       </c>
       <c r="K28" s="16">
@@ -2112,11 +2123,11 @@
         <v>40</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>620</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>820</v>
       </c>
       <c r="K29" s="16">
@@ -2158,11 +2169,11 @@
         <v>45</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>615</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>825</v>
       </c>
       <c r="K30" s="16">
@@ -2204,11 +2215,11 @@
         <v>40</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>810</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>630</v>
       </c>
       <c r="K31" s="16">
@@ -2250,11 +2261,11 @@
         <v>40</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>845</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>595</v>
       </c>
       <c r="K32" s="16">
@@ -2296,11 +2307,11 @@
         <v>40</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>905</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>535</v>
       </c>
       <c r="K33" s="16">
@@ -2342,11 +2353,11 @@
         <v>40</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>935</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>505</v>
       </c>
       <c r="K34" s="16">
@@ -3142,11 +3153,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3164,11 +3175,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3186,11 +3197,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3208,11 +3219,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3230,11 +3241,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3252,11 +3263,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3274,11 +3285,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3296,11 +3307,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3318,11 +3329,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3340,11 +3351,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3362,11 +3373,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3384,11 +3395,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3406,11 +3417,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3428,11 +3439,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3450,11 +3461,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3472,11 +3483,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3494,11 +3505,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3516,11 +3527,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3538,11 +3549,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3560,11 +3571,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3582,11 +3593,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3604,11 +3615,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3626,11 +3637,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3648,11 +3659,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3670,11 +3681,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3692,11 +3703,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3714,11 +3725,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3736,11 +3747,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3758,11 +3769,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3780,11 +3791,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3802,11 +3813,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3824,11 +3835,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3846,11 +3857,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3868,11 +3879,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3890,11 +3901,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3912,11 +3923,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3934,11 +3945,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3956,11 +3967,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3978,11 +3989,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4000,11 +4011,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4022,11 +4033,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4044,11 +4055,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4066,11 +4077,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4088,11 +4099,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4110,11 +4121,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4132,11 +4143,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4154,11 +4165,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4176,11 +4187,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4198,11 +4209,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4220,11 +4231,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4242,11 +4253,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4264,11 +4275,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4286,11 +4297,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4308,11 +4319,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4330,11 +4341,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4352,11 +4363,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4374,11 +4385,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4396,11 +4407,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4418,11 +4429,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4440,11 +4451,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4462,11 +4473,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4484,11 +4495,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4506,11 +4517,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4528,11 +4539,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4550,11 +4561,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4572,11 +4583,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4594,11 +4605,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4616,11 +4627,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4638,11 +4649,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4660,11 +4671,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4682,11 +4693,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4704,11 +4715,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4726,11 +4737,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4748,11 +4759,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4770,11 +4781,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4792,11 +4803,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4814,11 +4825,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4836,11 +4847,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4858,11 +4869,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4880,11 +4891,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4902,11 +4913,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4924,11 +4935,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4946,11 +4957,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4968,11 +4979,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4990,11 +5001,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5012,11 +5023,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5034,11 +5045,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5056,11 +5067,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5078,11 +5089,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5100,11 +5111,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5122,11 +5133,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5144,11 +5155,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5166,11 +5177,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5188,11 +5199,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5210,11 +5221,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5232,11 +5243,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5254,11 +5265,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5276,11 +5287,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5298,11 +5309,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5320,11 +5331,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5342,11 +5353,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5364,11 +5375,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5386,11 +5397,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5408,11 +5419,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5430,11 +5441,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5452,11 +5463,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5474,11 +5485,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5496,11 +5507,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5518,11 +5529,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5540,11 +5551,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5562,11 +5573,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5584,11 +5595,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5606,11 +5617,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5628,11 +5639,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5650,11 +5661,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5672,11 +5683,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5694,11 +5705,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5716,11 +5727,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5738,11 +5749,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5760,11 +5771,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5782,11 +5793,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5804,11 +5815,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5826,11 +5837,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5848,11 +5859,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5870,11 +5881,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5892,11 +5903,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5914,11 +5925,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5936,11 +5947,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5958,11 +5969,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5980,11 +5991,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6002,11 +6013,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6024,11 +6035,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6046,11 +6057,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6068,11 +6079,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6090,11 +6101,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6112,11 +6123,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6134,11 +6145,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6156,11 +6167,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6178,11 +6189,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6200,11 +6211,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6222,11 +6233,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6244,11 +6255,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6266,11 +6277,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6288,11 +6299,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6310,11 +6321,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6332,11 +6343,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6354,11 +6365,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6376,11 +6387,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6398,11 +6409,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6420,11 +6431,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6442,11 +6453,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6464,11 +6475,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6486,11 +6497,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6508,11 +6519,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6530,11 +6541,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6552,11 +6563,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6574,11 +6585,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6596,11 +6607,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6618,11 +6629,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6640,11 +6651,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6662,11 +6673,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6684,11 +6695,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6706,11 +6717,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6728,11 +6739,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6750,11 +6761,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6772,11 +6783,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6794,11 +6805,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6816,11 +6827,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6838,11 +6849,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6860,11 +6871,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6882,11 +6893,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6904,11 +6915,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6926,11 +6937,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6948,11 +6959,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6970,11 +6981,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6992,11 +7003,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7014,11 +7025,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7036,11 +7047,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7058,11 +7069,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7080,11 +7091,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7102,11 +7113,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7124,11 +7135,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7146,11 +7157,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7168,11 +7179,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7190,11 +7201,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7212,11 +7223,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7234,11 +7245,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7256,11 +7267,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7278,11 +7289,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7300,11 +7311,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7322,11 +7333,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7344,11 +7355,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7366,11 +7377,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7388,11 +7399,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7410,11 +7421,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7432,11 +7443,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7454,11 +7465,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7476,11 +7487,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7498,11 +7509,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7520,11 +7531,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7542,11 +7553,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7564,11 +7575,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7586,11 +7597,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7608,11 +7619,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7630,11 +7641,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7652,11 +7663,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7674,11 +7685,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7696,11 +7707,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7718,11 +7729,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7740,11 +7751,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7762,11 +7773,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7784,11 +7795,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7806,11 +7817,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7828,11 +7839,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7850,11 +7861,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7872,11 +7883,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7894,11 +7905,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7916,11 +7927,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7938,11 +7949,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7960,11 +7971,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7982,11 +7993,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8004,11 +8015,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8026,11 +8037,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8048,11 +8059,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8070,11 +8081,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8092,11 +8103,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8114,11 +8125,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8136,11 +8147,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8158,11 +8169,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8180,11 +8191,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8202,11 +8213,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8224,11 +8235,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8246,11 +8257,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8268,11 +8279,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8290,11 +8301,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8312,11 +8323,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8334,11 +8345,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8356,11 +8367,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8378,11 +8389,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8400,11 +8411,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8422,11 +8433,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8444,11 +8455,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8466,11 +8477,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8488,11 +8499,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8510,11 +8521,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8532,11 +8543,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8554,11 +8565,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8576,11 +8587,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8598,11 +8609,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8620,11 +8631,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8642,11 +8653,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8664,11 +8675,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8686,11 +8697,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8708,11 +8719,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8730,11 +8741,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8752,11 +8763,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8774,11 +8785,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8796,11 +8807,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8818,11 +8829,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8840,11 +8851,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8862,11 +8873,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8884,11 +8895,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8906,11 +8917,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8928,11 +8939,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8950,11 +8961,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8972,11 +8983,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8994,11 +9005,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9016,11 +9027,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9038,11 +9049,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9060,11 +9071,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9082,11 +9093,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9104,11 +9115,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9126,11 +9137,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9148,11 +9159,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9170,11 +9181,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9192,11 +9203,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9214,11 +9225,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9236,11 +9247,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9258,11 +9269,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9280,11 +9291,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9302,11 +9313,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9324,11 +9335,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9346,11 +9357,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9368,11 +9379,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9390,11 +9401,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9412,11 +9423,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9434,11 +9445,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9456,11 +9467,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9478,11 +9489,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9500,11 +9511,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9522,11 +9533,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9544,11 +9555,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9566,11 +9577,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9588,11 +9599,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9610,11 +9621,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9632,11 +9643,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9654,11 +9665,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9676,11 +9687,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9698,11 +9709,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9720,11 +9731,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9742,11 +9753,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9764,11 +9775,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9786,11 +9797,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9808,11 +9819,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9830,11 +9841,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9852,11 +9863,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9874,11 +9885,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9896,11 +9907,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9918,11 +9929,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9940,11 +9951,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9962,11 +9973,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9984,11 +9995,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10006,11 +10017,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10028,11 +10039,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10050,11 +10061,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10072,11 +10083,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10094,11 +10105,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10116,11 +10127,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10138,11 +10149,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10160,11 +10171,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10182,11 +10193,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10204,11 +10215,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10226,11 +10237,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10248,11 +10259,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10270,11 +10281,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10292,11 +10303,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10314,11 +10325,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10336,11 +10347,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10358,11 +10369,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10380,11 +10391,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10402,11 +10413,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10424,11 +10435,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10445,13 +10456,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J26 J35:J401">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J35:J401 J6:J26">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J34">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12607191.xlsx
+++ b/12607191.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,12 +389,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,7 +906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O401"/>
+  <dimension ref="A1:O414"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.77734375" customWidth="1"/>
@@ -922,77 +922,77 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-    </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12607191</v>
       </c>
-      <c r="G2" s="20"/>
-    </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <v>8</v>
       </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-    </row>
-    <row r="5" spans="1:15" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1062,11 +1062,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I82" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J82" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1082,87 +1082,87 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>46223</v>
-      </c>
-      <c r="B7" s="9">
-        <v>420</v>
-      </c>
-      <c r="C7" s="9">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B7" s="14">
+        <v>496</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>180</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>480</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
         <v>45</v>
       </c>
-      <c r="D7" s="9">
-        <v>120</v>
-      </c>
-      <c r="E7" s="9">
-        <v>90</v>
-      </c>
-      <c r="F7" s="9">
-        <v>180</v>
-      </c>
-      <c r="G7" s="9">
-        <v>3</v>
-      </c>
-      <c r="H7" s="9">
-        <v>30</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" ref="I7:I15" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v>885</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" ref="J7:J15" si="3">IF(I7="","",1440-I7)</f>
-        <v>555</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I7" s="15">
+        <f t="shared" ref="I7:I13" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>1251</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J13" si="3">IF(I7="","",1440-I7)</f>
+        <v>189</v>
+      </c>
+      <c r="K7" s="16">
+        <v>4</v>
+      </c>
+      <c r="L7" s="16">
+        <v>2</v>
+      </c>
+      <c r="M7" s="16">
+        <v>2</v>
+      </c>
+      <c r="N7" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46263</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="14">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C8" s="14">
         <v>20</v>
       </c>
       <c r="D8" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E8" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" s="14">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="2"/>
-        <v>1251</v>
+        <v>685</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="3"/>
-        <v>189</v>
+        <v>755</v>
       </c>
       <c r="K8" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8" s="16">
         <v>2</v>
@@ -1174,12 +1174,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46264</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
@@ -1188,47 +1188,47 @@
         <v>120</v>
       </c>
       <c r="E9" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G9" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="2"/>
-        <v>685</v>
+        <v>829</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="3"/>
-        <v>755</v>
+        <v>611</v>
       </c>
       <c r="K9" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="16">
         <v>2</v>
       </c>
       <c r="M9" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="B10" s="14">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C10" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D10" s="14">
         <v>120</v>
@@ -1237,27 +1237,27 @@
         <v>20</v>
       </c>
       <c r="F10" s="14">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G10" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="2"/>
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="3"/>
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="K10" s="16">
+        <v>4</v>
+      </c>
+      <c r="L10" s="16">
         <v>3</v>
-      </c>
-      <c r="L10" s="16">
-        <v>2</v>
       </c>
       <c r="M10" s="16">
         <v>3</v>
@@ -1266,122 +1266,122 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46266</v>
+        <v>46255</v>
       </c>
       <c r="B11" s="14">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C11" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D11" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="G11" s="14">
         <v>5</v>
       </c>
       <c r="H11" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="2"/>
-        <v>845</v>
+        <v>910</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="3"/>
-        <v>595</v>
+        <v>530</v>
       </c>
       <c r="K11" s="16">
         <v>4</v>
       </c>
       <c r="L11" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="16">
         <v>3</v>
       </c>
       <c r="N11" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46267</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C12" s="14">
         <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E12" s="14">
         <v>25</v>
       </c>
       <c r="F12" s="14">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="G12" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="14">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="2"/>
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="3"/>
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="K12" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12" s="16">
         <v>2</v>
       </c>
       <c r="M12" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46268</v>
+        <v>46257</v>
       </c>
       <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>100</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
         <v>400</v>
       </c>
-      <c r="C13" s="14">
-        <v>20</v>
-      </c>
-      <c r="D13" s="14">
-        <v>150</v>
-      </c>
-      <c r="E13" s="14">
-        <v>25</v>
-      </c>
-      <c r="F13" s="14">
-        <v>335</v>
-      </c>
       <c r="G13" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="2"/>
@@ -1392,70 +1392,70 @@
         <v>480</v>
       </c>
       <c r="K13" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="16">
         <v>2</v>
       </c>
       <c r="N13" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46269</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="C14" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E14" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14" s="14">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="G14" s="14">
         <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="2"/>
-        <v>960</v>
+        <f t="shared" si="0"/>
+        <v>1251</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="3"/>
-        <v>480</v>
+        <f t="shared" si="1"/>
+        <v>189</v>
       </c>
       <c r="K14" s="16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" s="16">
         <v>2</v>
       </c>
       <c r="N14" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46270</v>
+        <v>46257</v>
       </c>
       <c r="B15" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C15" s="14">
         <v>20</v>
@@ -1464,44 +1464,41 @@
         <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>685</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>755</v>
       </c>
       <c r="K15" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" s="17">
-        <v>3</v>
-      </c>
-      <c r="O15" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B16" s="14">
         <v>420</v>
@@ -1513,7 +1510,7 @@
         <v>120</v>
       </c>
       <c r="E16" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
         <v>200</v>
@@ -1522,44 +1519,44 @@
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="K16" s="16">
         <v>3</v>
       </c>
       <c r="L16" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" s="16">
         <v>3</v>
       </c>
       <c r="N16" s="17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46273</v>
+        <v>46259</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
         <v>120</v>
       </c>
       <c r="E17" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
         <v>225</v>
@@ -1572,17 +1569,17 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="K17" s="16">
+        <v>4</v>
+      </c>
+      <c r="L17" s="16">
         <v>3</v>
-      </c>
-      <c r="L17" s="16">
-        <v>2</v>
       </c>
       <c r="M17" s="16">
         <v>3</v>
@@ -1591,9 +1588,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="14">
         <v>420</v>
@@ -1602,10 +1599,10 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
         <v>300</v>
@@ -1614,21 +1611,21 @@
         <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="K18" s="16">
+        <v>4</v>
+      </c>
+      <c r="L18" s="16">
         <v>2</v>
-      </c>
-      <c r="L18" s="16">
-        <v>4</v>
       </c>
       <c r="M18" s="16">
         <v>3</v>
@@ -1637,18 +1634,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46275</v>
+        <v>46261</v>
       </c>
       <c r="B19" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C19" s="14">
         <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E19" s="14">
         <v>25</v>
@@ -1660,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="H19" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
@@ -1671,33 +1668,33 @@
         <v>480</v>
       </c>
       <c r="K19" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L19" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46276</v>
+        <v>46262</v>
       </c>
       <c r="B20" s="14">
         <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D20" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E20" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>400</v>
@@ -1710,28 +1707,28 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>960</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>480</v>
       </c>
       <c r="K20" s="16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L20" s="16">
         <v>3</v>
       </c>
       <c r="M20" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46277</v>
+        <v>46263</v>
       </c>
       <c r="B21" s="14">
         <v>420</v>
@@ -1743,50 +1740,50 @@
         <v>120</v>
       </c>
       <c r="E21" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F21" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G21" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>685</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>755</v>
       </c>
       <c r="K21" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="16">
         <v>3</v>
       </c>
       <c r="N21" s="17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46278</v>
+        <v>46264</v>
       </c>
       <c r="B22" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C22" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E22" s="14">
         <v>25</v>
@@ -1798,866 +1795,1179 @@
         <v>0</v>
       </c>
       <c r="H22" s="14">
+        <v>40</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" ref="I22:I28" si="4">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>685</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" ref="J22:J28" si="5">IF(I22="","",1440-I22)</f>
+        <v>755</v>
+      </c>
+      <c r="K22" s="16">
+        <v>2</v>
+      </c>
+      <c r="L22" s="16">
+        <v>2</v>
+      </c>
+      <c r="M22" s="16">
+        <v>2</v>
+      </c>
+      <c r="N22" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>49</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="4"/>
+        <v>829</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="5"/>
+        <v>611</v>
+      </c>
+      <c r="K23" s="16">
+        <v>3</v>
+      </c>
+      <c r="L23" s="16">
+        <v>2</v>
+      </c>
+      <c r="M23" s="16">
+        <v>3</v>
+      </c>
+      <c r="N23" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B24" s="14">
+        <v>425</v>
+      </c>
+      <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>225</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>40</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="4"/>
+        <v>845</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="5"/>
+        <v>595</v>
+      </c>
+      <c r="K24" s="16">
+        <v>4</v>
+      </c>
+      <c r="L24" s="16">
+        <v>3</v>
+      </c>
+      <c r="M24" s="16">
+        <v>3</v>
+      </c>
+      <c r="N24" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>100</v>
+      </c>
+      <c r="E25" s="14">
+        <v>25</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
         <v>45</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I25" s="15">
+        <f t="shared" si="4"/>
+        <v>910</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="5"/>
+        <v>530</v>
+      </c>
+      <c r="K25" s="16">
+        <v>4</v>
+      </c>
+      <c r="L25" s="16">
+        <v>2</v>
+      </c>
+      <c r="M25" s="16">
+        <v>3</v>
+      </c>
+      <c r="N25" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>150</v>
+      </c>
+      <c r="E26" s="14">
+        <v>25</v>
+      </c>
+      <c r="F26" s="14">
+        <v>335</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="4"/>
+        <v>960</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+      <c r="K26" s="16">
+        <v>2</v>
+      </c>
+      <c r="L26" s="16">
+        <v>2</v>
+      </c>
+      <c r="M26" s="16">
+        <v>2</v>
+      </c>
+      <c r="N26" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>100</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>400</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>40</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="4"/>
+        <v>960</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="5"/>
+        <v>480</v>
+      </c>
+      <c r="K27" s="16">
+        <v>1</v>
+      </c>
+      <c r="L27" s="16">
+        <v>3</v>
+      </c>
+      <c r="M27" s="16">
+        <v>2</v>
+      </c>
+      <c r="N27" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>50</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>45</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="4"/>
+        <v>685</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="5"/>
+        <v>755</v>
+      </c>
+      <c r="K28" s="16">
+        <v>3</v>
+      </c>
+      <c r="L28" s="16">
+        <v>3</v>
+      </c>
+      <c r="M28" s="16">
+        <v>3</v>
+      </c>
+      <c r="N28" s="17">
+        <v>3</v>
+      </c>
+      <c r="O28" s="18"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>25</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="1"/>
+        <v>615</v>
+      </c>
+      <c r="K29" s="16">
+        <v>3</v>
+      </c>
+      <c r="L29" s="16">
+        <v>3</v>
+      </c>
+      <c r="M29" s="16">
+        <v>3</v>
+      </c>
+      <c r="N29" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>225</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" si="0"/>
+        <v>855</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="1"/>
+        <v>585</v>
+      </c>
+      <c r="K30" s="16">
+        <v>3</v>
+      </c>
+      <c r="L30" s="16">
+        <v>2</v>
+      </c>
+      <c r="M30" s="16">
+        <v>3</v>
+      </c>
+      <c r="N30" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>300</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>40</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K31" s="16">
+        <v>2</v>
+      </c>
+      <c r="L31" s="16">
+        <v>4</v>
+      </c>
+      <c r="M31" s="16">
+        <v>3</v>
+      </c>
+      <c r="N31" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>20</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>25</v>
+      </c>
+      <c r="F32" s="14">
+        <v>335</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K32" s="16">
+        <v>4</v>
+      </c>
+      <c r="L32" s="16">
+        <v>4</v>
+      </c>
+      <c r="M32" s="16">
+        <v>3</v>
+      </c>
+      <c r="N32" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>400</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>40</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="K33" s="16">
+        <v>4</v>
+      </c>
+      <c r="L33" s="16">
+        <v>3</v>
+      </c>
+      <c r="M33" s="16">
+        <v>3</v>
+      </c>
+      <c r="N33" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>40</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="0"/>
+        <v>620</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="K34" s="16">
+        <v>2</v>
+      </c>
+      <c r="L34" s="16">
+        <v>2</v>
+      </c>
+      <c r="M34" s="16">
+        <v>3</v>
+      </c>
+      <c r="N34" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>25</v>
+      </c>
+      <c r="D35" s="14">
+        <v>100</v>
+      </c>
+      <c r="E35" s="14">
+        <v>25</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>45</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
         <v>615</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>825</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K35" s="16">
         <v>2</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L35" s="16">
         <v>2</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M35" s="16">
         <v>3</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N35" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
         <v>46279</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B36" s="14">
         <v>420</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C36" s="14">
         <v>25</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D36" s="14">
         <v>100</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E36" s="14">
         <v>25</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F36" s="14">
         <v>200</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G36" s="14">
         <v>4</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H36" s="14">
         <v>40</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K36" s="16">
         <v>3</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L36" s="16">
         <v>3</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M36" s="16">
         <v>3</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N36" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
         <v>46280</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B37" s="14">
         <v>420</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C37" s="14">
         <v>20</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D37" s="14">
         <v>120</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E37" s="14">
         <v>20</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F37" s="14">
         <v>225</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G37" s="14">
         <v>5</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H37" s="14">
         <v>40</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
         <v>845</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>595</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K37" s="16">
         <v>3</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L37" s="16">
         <v>3</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M37" s="16">
         <v>3</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N37" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
         <v>46281</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B38" s="14">
         <v>420</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C38" s="14">
         <v>20</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D38" s="14">
         <v>100</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E38" s="14">
         <v>25</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F38" s="14">
         <v>300</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G38" s="14">
         <v>6</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H38" s="14">
         <v>40</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>905</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>535</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K38" s="16">
         <v>3</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L38" s="16">
         <v>2</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M38" s="16">
         <v>3</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N38" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
         <v>46282</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B39" s="14">
         <v>420</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C39" s="14">
         <v>20</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D39" s="14">
         <v>100</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E39" s="14">
         <v>20</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F39" s="14">
         <v>335</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G39" s="14">
         <v>7</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H39" s="14">
         <v>40</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>935</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K39" s="16">
         <v>3</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L39" s="16">
         <v>3</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M39" s="16">
         <v>2</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N39" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
         <v>46283</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B40" s="14">
         <v>420</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C40" s="14">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D40" s="14">
         <v>120</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E40" s="14">
         <v>25</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F40" s="14">
         <v>335</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G40" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H40" s="14">
         <v>40</v>
       </c>
-      <c r="I27" s="15">
-        <f t="shared" ref="I27:I34" si="4">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+      <c r="I40" s="15">
+        <f t="shared" ref="I40:I47" si="6">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
         <v>960</v>
       </c>
-      <c r="J27" s="15">
-        <f t="shared" ref="J27:J34" si="5">IF(I27="","",1440-I27)</f>
+      <c r="J40" s="15">
+        <f t="shared" ref="J40:J47" si="7">IF(I40="","",1440-I40)</f>
         <v>480</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K40" s="16">
         <v>4</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L40" s="16">
         <v>4</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M40" s="16">
         <v>3</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N40" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
         <v>46284</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B41" s="14">
         <v>420</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C41" s="14">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D41" s="14">
         <v>120</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E41" s="14">
         <v>30</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F41" s="14">
         <v>400</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G41" s="14">
         <v>7</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H41" s="14">
         <v>40</v>
       </c>
-      <c r="I28" s="15">
-        <f t="shared" si="4"/>
+      <c r="I41" s="15">
+        <f t="shared" si="6"/>
         <v>1030</v>
       </c>
-      <c r="J28" s="15">
-        <f t="shared" si="5"/>
+      <c r="J41" s="15">
+        <f t="shared" si="7"/>
         <v>410</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K41" s="16">
         <v>4</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L41" s="16">
         <v>3</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M41" s="16">
         <v>3</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N41" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
         <v>46285</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B42" s="14">
         <v>420</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C42" s="14">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D42" s="14">
         <v>120</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E42" s="14">
         <v>20</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F42" s="14">
         <v>0</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G42" s="14">
         <v>0</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H42" s="14">
         <v>40</v>
       </c>
-      <c r="I29" s="15">
-        <f t="shared" si="4"/>
+      <c r="I42" s="15">
+        <f t="shared" si="6"/>
         <v>620</v>
       </c>
-      <c r="J29" s="15">
-        <f t="shared" si="5"/>
+      <c r="J42" s="15">
+        <f t="shared" si="7"/>
         <v>820</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K42" s="16">
         <v>2</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L42" s="16">
         <v>2</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M42" s="16">
         <v>3</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N42" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
         <v>46286</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B43" s="14">
         <v>420</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C43" s="14">
         <v>25</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D43" s="14">
         <v>100</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E43" s="14">
         <v>25</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F43" s="14">
         <v>0</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G43" s="14">
         <v>0</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H43" s="14">
         <v>45</v>
       </c>
-      <c r="I30" s="15">
-        <f t="shared" si="4"/>
+      <c r="I43" s="15">
+        <f t="shared" si="6"/>
         <v>615</v>
       </c>
-      <c r="J30" s="15">
-        <f t="shared" si="5"/>
+      <c r="J43" s="15">
+        <f t="shared" si="7"/>
         <v>825</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K43" s="16">
         <v>2</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L43" s="16">
         <v>2</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M43" s="16">
         <v>3</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N43" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
         <v>46287</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B44" s="14">
         <v>420</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C44" s="14">
         <v>25</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D44" s="14">
         <v>100</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E44" s="14">
         <v>25</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F44" s="14">
         <v>200</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G44" s="14">
         <v>4</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H44" s="14">
         <v>40</v>
       </c>
-      <c r="I31" s="15">
-        <f t="shared" si="4"/>
+      <c r="I44" s="15">
+        <f t="shared" si="6"/>
         <v>810</v>
       </c>
-      <c r="J31" s="15">
-        <f t="shared" si="5"/>
+      <c r="J44" s="15">
+        <f t="shared" si="7"/>
         <v>630</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K44" s="16">
         <v>3</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L44" s="16">
         <v>3</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M44" s="16">
         <v>3</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N44" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
         <v>46288</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B45" s="14">
         <v>420</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C45" s="14">
         <v>20</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D45" s="14">
         <v>120</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E45" s="14">
         <v>20</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F45" s="14">
         <v>225</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G45" s="14">
         <v>5</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H45" s="14">
         <v>40</v>
       </c>
-      <c r="I32" s="15">
-        <f t="shared" si="4"/>
+      <c r="I45" s="15">
+        <f t="shared" si="6"/>
         <v>845</v>
       </c>
-      <c r="J32" s="15">
-        <f t="shared" si="5"/>
+      <c r="J45" s="15">
+        <f t="shared" si="7"/>
         <v>595</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K45" s="16">
         <v>3</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L45" s="16">
         <v>3</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M45" s="16">
         <v>3</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N45" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
         <v>46289</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B46" s="14">
         <v>420</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C46" s="14">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D46" s="14">
         <v>100</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E46" s="14">
         <v>25</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F46" s="14">
         <v>300</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G46" s="14">
         <v>6</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H46" s="14">
         <v>40</v>
       </c>
-      <c r="I33" s="15">
-        <f t="shared" si="4"/>
+      <c r="I46" s="15">
+        <f t="shared" si="6"/>
         <v>905</v>
       </c>
-      <c r="J33" s="15">
-        <f t="shared" si="5"/>
+      <c r="J46" s="15">
+        <f t="shared" si="7"/>
         <v>535</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K46" s="16">
         <v>3</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L46" s="16">
         <v>2</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M46" s="16">
         <v>3</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N46" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
         <v>46290</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B47" s="14">
         <v>420</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C47" s="14">
         <v>20</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D47" s="14">
         <v>100</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E47" s="14">
         <v>20</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F47" s="14">
         <v>335</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G47" s="14">
         <v>7</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H47" s="14">
         <v>40</v>
       </c>
-      <c r="I34" s="15">
-        <f t="shared" si="4"/>
+      <c r="I47" s="15">
+        <f t="shared" si="6"/>
         <v>935</v>
       </c>
-      <c r="J34" s="15">
-        <f t="shared" si="5"/>
+      <c r="J47" s="15">
+        <f t="shared" si="7"/>
         <v>505</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K47" s="16">
         <v>3</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L47" s="16">
         <v>3</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M47" s="16">
         <v>2</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N47" s="17">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
@@ -3153,11 +3463,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3175,11 +3485,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3197,11 +3507,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3219,11 +3529,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3241,11 +3551,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3263,11 +3573,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3285,11 +3595,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3307,11 +3617,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3329,11 +3639,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3351,11 +3661,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3373,11 +3683,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3395,11 +3705,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3417,11 +3727,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3439,11 +3749,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I83:I146" si="8">IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J83:J146" si="9">IF(I83="","",1440-I83)</f>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3461,11 +3771,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3483,11 +3793,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3505,11 +3815,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3527,11 +3837,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3549,11 +3859,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3571,11 +3881,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3593,11 +3903,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3615,11 +3925,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3637,11 +3947,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3659,11 +3969,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3681,11 +3991,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3703,11 +4013,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3725,11 +4035,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3747,11 +4057,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3769,11 +4079,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3791,11 +4101,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3813,11 +4123,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3835,11 +4145,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3857,11 +4167,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3879,11 +4189,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3901,11 +4211,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3923,11 +4233,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3945,11 +4255,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3967,11 +4277,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3989,11 +4299,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4011,11 +4321,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4033,11 +4343,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4055,11 +4365,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4077,11 +4387,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4099,11 +4409,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4121,11 +4431,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4143,11 +4453,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4165,11 +4475,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4187,11 +4497,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4209,11 +4519,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4231,11 +4541,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4253,11 +4563,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4275,11 +4585,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4297,11 +4607,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4319,11 +4629,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4341,11 +4651,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4363,11 +4673,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4385,11 +4695,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4407,11 +4717,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4429,11 +4739,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4451,11 +4761,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4473,11 +4783,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4495,11 +4805,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4517,11 +4827,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4539,11 +4849,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4561,11 +4871,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4847,11 +5157,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I147:I210" si="10">IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J147:J210" si="11">IF(I147="","",1440-I147)</f>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4869,11 +5179,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4891,11 +5201,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4913,11 +5223,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4935,11 +5245,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4957,11 +5267,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4979,11 +5289,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5001,11 +5311,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5023,11 +5333,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5045,11 +5355,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5067,11 +5377,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5089,11 +5399,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5111,11 +5421,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5133,11 +5443,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5155,11 +5465,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5177,11 +5487,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5199,11 +5509,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5221,11 +5531,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5243,11 +5553,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5265,11 +5575,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5287,11 +5597,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5309,11 +5619,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5331,11 +5641,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5353,11 +5663,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5375,11 +5685,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5397,11 +5707,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5419,11 +5729,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5441,11 +5751,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5463,11 +5773,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5485,11 +5795,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5507,11 +5817,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5529,11 +5839,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5551,11 +5861,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5573,11 +5883,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5595,11 +5905,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5617,11 +5927,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5639,11 +5949,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5661,11 +5971,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5683,11 +5993,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5705,11 +6015,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5727,11 +6037,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5749,11 +6059,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5771,11 +6081,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5793,11 +6103,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5815,11 +6125,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5837,11 +6147,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5859,11 +6169,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5881,11 +6191,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5903,11 +6213,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5925,11 +6235,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5947,11 +6257,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5969,11 +6279,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6255,11 +6565,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I211:I274" si="12">IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J211:J274" si="13">IF(I211="","",1440-I211)</f>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6277,11 +6587,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6299,11 +6609,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6321,11 +6631,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6343,11 +6653,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6365,11 +6675,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6387,11 +6697,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6409,11 +6719,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6431,11 +6741,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6453,11 +6763,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6475,11 +6785,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6497,11 +6807,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6519,11 +6829,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6541,11 +6851,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6563,11 +6873,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6585,11 +6895,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6607,11 +6917,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6629,11 +6939,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6651,11 +6961,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6673,11 +6983,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6695,11 +7005,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6717,11 +7027,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6739,11 +7049,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6761,11 +7071,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6783,11 +7093,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6805,11 +7115,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6827,11 +7137,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6849,11 +7159,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6871,11 +7181,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6893,11 +7203,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6915,11 +7225,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6937,11 +7247,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6959,11 +7269,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6981,11 +7291,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7003,11 +7313,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7025,11 +7335,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7047,11 +7357,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7069,11 +7379,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7091,11 +7401,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7113,11 +7423,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7135,11 +7445,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7157,11 +7467,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7179,11 +7489,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7201,11 +7511,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7223,11 +7533,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7245,11 +7555,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7267,11 +7577,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7289,11 +7599,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7311,11 +7621,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7333,11 +7643,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7355,11 +7665,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7377,11 +7687,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7663,11 +7973,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I275:I338" si="14">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J275:J338" si="15">IF(I275="","",1440-I275)</f>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7685,11 +7995,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7707,11 +8017,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7729,11 +8039,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7751,11 +8061,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7773,11 +8083,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7795,11 +8105,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7817,11 +8127,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7839,11 +8149,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7861,11 +8171,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7883,11 +8193,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7905,11 +8215,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7927,11 +8237,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7949,11 +8259,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7971,11 +8281,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7993,11 +8303,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8015,11 +8325,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8037,11 +8347,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8059,11 +8369,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8081,11 +8391,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8103,11 +8413,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8125,11 +8435,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8147,11 +8457,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8169,11 +8479,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8191,11 +8501,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8213,11 +8523,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8235,11 +8545,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8257,11 +8567,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8279,11 +8589,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8301,11 +8611,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8323,11 +8633,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8345,11 +8655,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8367,11 +8677,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8389,11 +8699,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8411,11 +8721,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8433,11 +8743,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8455,11 +8765,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8477,11 +8787,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8499,11 +8809,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8521,11 +8831,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8543,11 +8853,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8565,11 +8875,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8587,11 +8897,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8609,11 +8919,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8631,11 +8941,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8653,11 +8963,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8675,11 +8985,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8697,11 +9007,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8719,11 +9029,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8741,11 +9051,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8763,11 +9073,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8785,11 +9095,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9071,11 +9381,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I339:I402" si="16">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J339:J402" si="17">IF(I339="","",1440-I339)</f>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9093,11 +9403,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9115,11 +9425,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9137,11 +9447,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9159,11 +9469,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9181,11 +9491,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9203,11 +9513,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9225,11 +9535,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9247,11 +9557,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9269,11 +9579,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9291,11 +9601,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9313,11 +9623,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9335,11 +9645,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9357,11 +9667,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9379,11 +9689,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9401,11 +9711,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9423,11 +9733,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9445,11 +9755,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9467,11 +9777,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9489,11 +9799,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9511,11 +9821,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9533,11 +9843,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9555,11 +9865,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9577,11 +9887,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9599,11 +9909,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9621,11 +9931,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9643,11 +9953,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9665,11 +9975,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9687,11 +9997,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9709,11 +10019,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9731,11 +10041,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9753,11 +10063,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9775,11 +10085,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9797,11 +10107,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9819,11 +10129,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9841,11 +10151,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9863,11 +10173,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9885,11 +10195,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9907,11 +10217,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9929,11 +10239,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9951,11 +10261,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9973,11 +10283,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9995,11 +10305,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10017,11 +10327,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10039,11 +10349,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10061,11 +10371,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10083,11 +10393,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10105,11 +10415,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10127,11 +10437,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10149,11 +10459,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10171,11 +10481,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10193,11 +10503,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10447,6 +10757,292 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" ref="I403:I414" si="18">IF(SUM(B403:F403,H403)=0,"",SUM(B403:F403,H403))</f>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" ref="J403:J414" si="19">IF(I403="","",1440-I403)</f>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A406" s="13"/>
+      <c r="B406" s="14"/>
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J406" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K406" s="16"/>
+      <c r="L406" s="16"/>
+      <c r="M406" s="16"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A407" s="13"/>
+      <c r="B407" s="14"/>
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J407" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K407" s="16"/>
+      <c r="L407" s="16"/>
+      <c r="M407" s="16"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A408" s="13"/>
+      <c r="B408" s="14"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J408" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K408" s="16"/>
+      <c r="L408" s="16"/>
+      <c r="M408" s="16"/>
+      <c r="N408" s="17"/>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A409" s="13"/>
+      <c r="B409" s="14"/>
+      <c r="C409" s="14"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="14"/>
+      <c r="F409" s="14"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="I409" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J409" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K409" s="16"/>
+      <c r="L409" s="16"/>
+      <c r="M409" s="16"/>
+      <c r="N409" s="17"/>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A410" s="13"/>
+      <c r="B410" s="14"/>
+      <c r="C410" s="14"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="14"/>
+      <c r="F410" s="14"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="I410" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J410" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K410" s="16"/>
+      <c r="L410" s="16"/>
+      <c r="M410" s="16"/>
+      <c r="N410" s="17"/>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A411" s="13"/>
+      <c r="B411" s="14"/>
+      <c r="C411" s="14"/>
+      <c r="D411" s="14"/>
+      <c r="E411" s="14"/>
+      <c r="F411" s="14"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="I411" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J411" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K411" s="16"/>
+      <c r="L411" s="16"/>
+      <c r="M411" s="16"/>
+      <c r="N411" s="17"/>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A412" s="13"/>
+      <c r="B412" s="14"/>
+      <c r="C412" s="14"/>
+      <c r="D412" s="14"/>
+      <c r="E412" s="14"/>
+      <c r="F412" s="14"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="I412" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J412" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K412" s="16"/>
+      <c r="L412" s="16"/>
+      <c r="M412" s="16"/>
+      <c r="N412" s="17"/>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A413" s="13"/>
+      <c r="B413" s="14"/>
+      <c r="C413" s="14"/>
+      <c r="D413" s="14"/>
+      <c r="E413" s="14"/>
+      <c r="F413" s="14"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="I413" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J413" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K413" s="16"/>
+      <c r="L413" s="16"/>
+      <c r="M413" s="16"/>
+      <c r="N413" s="17"/>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A414" s="13"/>
+      <c r="B414" s="14"/>
+      <c r="C414" s="14"/>
+      <c r="D414" s="14"/>
+      <c r="E414" s="14"/>
+      <c r="F414" s="14"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="I414" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J414" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="K414" s="16"/>
+      <c r="L414" s="16"/>
+      <c r="M414" s="16"/>
+      <c r="N414" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10456,26 +11052,31 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J35:J401 J6:J26">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J48:J414 J6 J14:J39">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27:J34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J40:J47">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+  <conditionalFormatting sqref="J7:J13">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K414">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L414">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M414">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
